--- a/onprc_ehr/resources/web/onprc_ehr/templates/ClinicalProcessingTemplate.xlsx
+++ b/onprc_ehr/resources/web/onprc_ehr/templates/ClinicalProcessingTemplate.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blasar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7746A37-3AD6-554F-8429-DB0E5BD7DF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C98B6B7-3F68-4A44-9944-17BB0BC42794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="V0mH21jSP57WeMvfm2GZf/CFapX9PbyX3c7CLbaowv65HEOfZYZks22oton1PO1KhMKfP/Yy+b48PowhVvmdMw==" workbookSaltValue="7RYukLmSAngqyTzJhGnEpg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="2280" windowWidth="29260" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5720" yWindow="920" windowWidth="30600" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ClinProcessing Entry Template" sheetId="6" r:id="rId1"/>
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ClinProcessing Entry Template'!$A$80:$J$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Drop-down lists'!$G$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="125">
   <si>
     <t>Id</t>
   </si>
@@ -410,6 +411,9 @@
   </si>
   <si>
     <t>Applies to Preg column with "No" value</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -894,7 +898,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:J581"/>
+  <dimension ref="A1:J720"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="12" customWidth="1"/>
@@ -3638,56 +3642,473 @@
       <c r="A569" s="9"/>
       <c r="E569" s="8"/>
     </row>
+    <row r="570" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H570" s="7"/>
+    </row>
     <row r="571" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H571" s="15"/>
+      <c r="H571" s="7"/>
       <c r="I571" s="15"/>
     </row>
     <row r="572" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H572" s="15"/>
+      <c r="H572" s="7"/>
       <c r="I572" s="15"/>
     </row>
     <row r="573" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H573" s="15"/>
+      <c r="H573" s="7"/>
       <c r="I573" s="15"/>
     </row>
     <row r="574" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H574" s="15"/>
+      <c r="H574" s="7"/>
       <c r="I574" s="15"/>
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H575" s="15"/>
+      <c r="H575" s="7"/>
       <c r="I575" s="15"/>
     </row>
     <row r="576" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="H576" s="15"/>
+      <c r="H576" s="7"/>
       <c r="I576" s="15"/>
     </row>
     <row r="577" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H577" s="15"/>
+      <c r="H577" s="7"/>
       <c r="I577" s="15"/>
     </row>
     <row r="578" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H578" s="15"/>
+      <c r="H578" s="7"/>
       <c r="I578" s="15"/>
     </row>
     <row r="579" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H579" s="15"/>
+      <c r="H579" s="7"/>
       <c r="I579" s="15"/>
     </row>
     <row r="580" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H580" s="15"/>
+      <c r="H580" s="7"/>
       <c r="I580" s="15"/>
     </row>
     <row r="581" spans="8:9" x14ac:dyDescent="0.2">
-      <c r="H581" s="15"/>
+      <c r="H581" s="7"/>
       <c r="I581" s="15"/>
+    </row>
+    <row r="582" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H582" s="7"/>
+    </row>
+    <row r="583" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H583" s="7"/>
+    </row>
+    <row r="584" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H584" s="7"/>
+    </row>
+    <row r="585" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H585" s="7"/>
+    </row>
+    <row r="586" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H586" s="7"/>
+    </row>
+    <row r="587" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H587" s="7"/>
+    </row>
+    <row r="588" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H588" s="7"/>
+    </row>
+    <row r="589" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H589" s="7"/>
+    </row>
+    <row r="590" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H590" s="7"/>
+    </row>
+    <row r="591" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H591" s="7"/>
+    </row>
+    <row r="592" spans="8:9" x14ac:dyDescent="0.2">
+      <c r="H592" s="7"/>
+    </row>
+    <row r="593" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H593" s="7"/>
+    </row>
+    <row r="594" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H594" s="7"/>
+    </row>
+    <row r="595" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H595" s="7"/>
+    </row>
+    <row r="596" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H596" s="7"/>
+    </row>
+    <row r="597" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H597" s="7"/>
+    </row>
+    <row r="598" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H598" s="7"/>
+    </row>
+    <row r="599" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H599" s="7"/>
+    </row>
+    <row r="600" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H600" s="7"/>
+    </row>
+    <row r="601" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H601" s="7"/>
+    </row>
+    <row r="602" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H602" s="7"/>
+    </row>
+    <row r="603" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H603" s="7"/>
+    </row>
+    <row r="604" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H604" s="7"/>
+    </row>
+    <row r="605" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H605" s="7"/>
+    </row>
+    <row r="606" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H606" s="7"/>
+    </row>
+    <row r="607" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H607" s="7"/>
+    </row>
+    <row r="608" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H608" s="7"/>
+    </row>
+    <row r="609" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H609" s="7"/>
+    </row>
+    <row r="610" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H610" s="7"/>
+    </row>
+    <row r="611" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H611" s="7"/>
+    </row>
+    <row r="612" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H612" s="7"/>
+    </row>
+    <row r="613" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H613" s="7"/>
+    </row>
+    <row r="614" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H614" s="7"/>
+    </row>
+    <row r="615" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H615" s="7"/>
+    </row>
+    <row r="616" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H616" s="7"/>
+    </row>
+    <row r="617" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H617" s="7"/>
+    </row>
+    <row r="618" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H618" s="7"/>
+    </row>
+    <row r="619" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H619" s="7"/>
+    </row>
+    <row r="620" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H620" s="7"/>
+    </row>
+    <row r="621" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H621" s="7"/>
+    </row>
+    <row r="622" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H622" s="7"/>
+    </row>
+    <row r="623" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H623" s="7"/>
+    </row>
+    <row r="624" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H624" s="7"/>
+    </row>
+    <row r="625" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H625" s="7"/>
+    </row>
+    <row r="626" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H626" s="7"/>
+    </row>
+    <row r="627" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H627" s="7"/>
+    </row>
+    <row r="628" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H628" s="7"/>
+    </row>
+    <row r="629" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H629" s="7"/>
+    </row>
+    <row r="630" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H630" s="7"/>
+    </row>
+    <row r="631" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H631" s="7"/>
+    </row>
+    <row r="632" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H632" s="7"/>
+    </row>
+    <row r="633" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H633" s="7"/>
+    </row>
+    <row r="634" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H634" s="7"/>
+    </row>
+    <row r="635" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H635" s="7"/>
+    </row>
+    <row r="636" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H636" s="7"/>
+    </row>
+    <row r="637" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H637" s="7"/>
+    </row>
+    <row r="638" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H638" s="7"/>
+    </row>
+    <row r="639" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H639" s="7"/>
+    </row>
+    <row r="640" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H640" s="7"/>
+    </row>
+    <row r="641" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H641" s="7"/>
+    </row>
+    <row r="642" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H642" s="7"/>
+    </row>
+    <row r="643" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H643" s="7"/>
+    </row>
+    <row r="644" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H644" s="7"/>
+    </row>
+    <row r="645" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H645" s="7"/>
+    </row>
+    <row r="646" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H646" s="7"/>
+    </row>
+    <row r="647" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H647" s="7"/>
+    </row>
+    <row r="648" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H648" s="7"/>
+    </row>
+    <row r="649" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H649" s="7"/>
+    </row>
+    <row r="650" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H650" s="7"/>
+    </row>
+    <row r="651" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H651" s="7"/>
+    </row>
+    <row r="652" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H652" s="7"/>
+    </row>
+    <row r="653" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H653" s="7"/>
+    </row>
+    <row r="654" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H654" s="7"/>
+    </row>
+    <row r="655" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H655" s="7"/>
+    </row>
+    <row r="656" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H656" s="7"/>
+    </row>
+    <row r="657" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H657" s="7"/>
+    </row>
+    <row r="658" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H658" s="7"/>
+    </row>
+    <row r="659" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H659" s="7"/>
+    </row>
+    <row r="660" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H660" s="7"/>
+    </row>
+    <row r="661" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H661" s="7"/>
+    </row>
+    <row r="662" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H662" s="7"/>
+    </row>
+    <row r="663" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H663" s="7"/>
+    </row>
+    <row r="664" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H664" s="7"/>
+    </row>
+    <row r="665" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H665" s="7"/>
+    </row>
+    <row r="666" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H666" s="7"/>
+    </row>
+    <row r="667" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H667" s="7"/>
+    </row>
+    <row r="668" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H668" s="7"/>
+    </row>
+    <row r="669" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H669" s="7"/>
+    </row>
+    <row r="670" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H670" s="7"/>
+    </row>
+    <row r="671" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H671" s="7"/>
+    </row>
+    <row r="672" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H672" s="7"/>
+    </row>
+    <row r="673" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H673" s="7"/>
+    </row>
+    <row r="674" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H674" s="7"/>
+    </row>
+    <row r="675" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H675" s="7"/>
+    </row>
+    <row r="676" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H676" s="7"/>
+    </row>
+    <row r="677" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H677" s="7"/>
+    </row>
+    <row r="678" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H678" s="7"/>
+    </row>
+    <row r="679" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H679" s="7"/>
+    </row>
+    <row r="680" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H680" s="7"/>
+    </row>
+    <row r="681" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H681" s="7"/>
+    </row>
+    <row r="682" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H682" s="7"/>
+    </row>
+    <row r="683" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H683" s="7"/>
+    </row>
+    <row r="684" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H684" s="7"/>
+    </row>
+    <row r="685" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H685" s="7"/>
+    </row>
+    <row r="686" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H686" s="7"/>
+    </row>
+    <row r="687" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H687" s="7"/>
+    </row>
+    <row r="688" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H688" s="7"/>
+    </row>
+    <row r="689" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H689" s="7"/>
+    </row>
+    <row r="690" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H690" s="7"/>
+    </row>
+    <row r="691" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H691" s="7"/>
+    </row>
+    <row r="692" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H692" s="7"/>
+    </row>
+    <row r="693" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H693" s="7"/>
+    </row>
+    <row r="694" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H694" s="7"/>
+    </row>
+    <row r="695" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H695" s="7"/>
+    </row>
+    <row r="696" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H696" s="7"/>
+    </row>
+    <row r="697" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H697" s="7"/>
+    </row>
+    <row r="698" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H698" s="7"/>
+    </row>
+    <row r="699" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H699" s="7"/>
+    </row>
+    <row r="700" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H700" s="7"/>
+    </row>
+    <row r="701" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H701" s="7"/>
+    </row>
+    <row r="702" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H702" s="7"/>
+    </row>
+    <row r="703" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H703" s="7"/>
+    </row>
+    <row r="704" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H704" s="7"/>
+    </row>
+    <row r="705" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H705" s="7"/>
+    </row>
+    <row r="706" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H706" s="7"/>
+    </row>
+    <row r="707" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H707" s="7"/>
+    </row>
+    <row r="708" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H708" s="7"/>
+    </row>
+    <row r="710" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H710" s="15"/>
+    </row>
+    <row r="711" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H711" s="15"/>
+    </row>
+    <row r="712" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H712" s="15"/>
+    </row>
+    <row r="713" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H713" s="15"/>
+    </row>
+    <row r="714" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H714" s="15"/>
+    </row>
+    <row r="715" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H715" s="15"/>
+    </row>
+    <row r="716" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H716" s="15"/>
+    </row>
+    <row r="717" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H717" s="15"/>
+    </row>
+    <row r="718" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H718" s="15"/>
+    </row>
+    <row r="719" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H719" s="15"/>
+    </row>
+    <row r="720" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H720" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>'Drop-down lists'!#REF!</xm:f>
@@ -3718,17 +4139,23 @@
           </x14:formula1>
           <xm:sqref>G69:G569</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
-          <x14:formula1>
-            <xm:f>'Drop-down lists'!$G$2:$G$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>H69:H569</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
           <x14:formula1>
             <xm:f>'Drop-down lists'!$H$2:$H$3</xm:f>
           </x14:formula1>
           <xm:sqref>I69:I569</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
+          <x14:formula1>
+            <xm:f>'Drop-down lists'!$G$2:$G$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>H69 H209:H708</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{25E1E495-68A7-8D49-B0E7-753B3990CBA7}">
+          <x14:formula1>
+            <xm:f>'Drop-down lists'!$G$2:$G$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>H70:H208</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3848,7 +4275,9 @@
         <v>3</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">

--- a/onprc_ehr/resources/web/onprc_ehr/templates/ClinicalProcessingTemplate.xlsx
+++ b/onprc_ehr/resources/web/onprc_ehr/templates/ClinicalProcessingTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blasar/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C98B6B7-3F68-4A44-9944-17BB0BC42794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4B6F4B-8562-3946-A936-D3ECBBD18399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="V0mH21jSP57WeMvfm2GZf/CFapX9PbyX3c7CLbaowv65HEOfZYZks22oton1PO1KhMKfP/Yy+b48PowhVvmdMw==" workbookSaltValue="7RYukLmSAngqyTzJhGnEpg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="5720" yWindow="920" windowWidth="30600" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -1599,12 +1599,12 @@
         <v>53</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="13"/>
       <c r="B67" s="3"/>
       <c r="D67" s="15"/>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="13" t="s">
         <v>0</v>
       </c>
@@ -4155,7 +4155,7 @@
           <x14:formula1>
             <xm:f>'Drop-down lists'!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H70:H208</xm:sqref>
+          <xm:sqref>H167:H208 H70:H166</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/onprc_ehr/resources/web/onprc_ehr/templates/ClinicalProcessingTemplate.xlsx
+++ b/onprc_ehr/resources/web/onprc_ehr/templates/ClinicalProcessingTemplate.xlsx
@@ -5,13 +5,13 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blasar/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/tmp/blasarVolumes/blasar/XML_Project/Heather_Panaro/ClinicalProcessing_TPR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A4B6F4B-8562-3946-A936-D3ECBBD18399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67BF84A-E68A-4241-B673-2A22004E0B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="V0mH21jSP57WeMvfm2GZf/CFapX9PbyX3c7CLbaowv65HEOfZYZks22oton1PO1KhMKfP/Yy+b48PowhVvmdMw==" workbookSaltValue="7RYukLmSAngqyTzJhGnEpg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="5720" yWindow="920" windowWidth="30600" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10840" yWindow="1900" windowWidth="30600" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ClinProcessing Entry Template" sheetId="6" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="131">
   <si>
     <t>Id</t>
   </si>
@@ -155,24 +155,12 @@
     <t>cullin</t>
   </si>
   <si>
-    <t>Heather Sidener</t>
-  </si>
-  <si>
-    <t>sidener</t>
-  </si>
-  <si>
     <t>Jeff Stanton</t>
   </si>
   <si>
     <t>stantoje</t>
   </si>
   <si>
-    <t>Kamm Prongay</t>
-  </si>
-  <si>
-    <t>prongayk</t>
-  </si>
-  <si>
     <t>Rhonda MacAllister</t>
   </si>
   <si>
@@ -414,13 +402,43 @@
   </si>
   <si>
     <t>No</t>
+  </si>
+  <si>
+    <t>Drew Martin</t>
+  </si>
+  <si>
+    <t>martilau</t>
+  </si>
+  <si>
+    <t>Eden Doh</t>
+  </si>
+  <si>
+    <t>dohe</t>
+  </si>
+  <si>
+    <t>Joshua Taylor</t>
+  </si>
+  <si>
+    <t>tayljosh</t>
+  </si>
+  <si>
+    <t>Kendall Lewis</t>
+  </si>
+  <si>
+    <t>lewisken</t>
+  </si>
+  <si>
+    <t>Monica Stroyer</t>
+  </si>
+  <si>
+    <t>shroyer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -469,6 +487,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -510,7 +534,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -591,6 +615,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -935,10 +960,10 @@
         <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C5" s="11" t="str">
-        <f>VLOOKUP(B5,'Drop-down lists'!A2:B12,2,FALSE)</f>
+        <f>VLOOKUP(B5,'Drop-down lists'!A2:B15,2,FALSE)</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -948,7 +973,7 @@
     </row>
     <row r="7" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="18"/>
@@ -965,32 +990,32 @@
         <v>0</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -998,10 +1023,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1009,10 +1034,10 @@
         <v>16</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1023,29 +1048,29 @@
         <v>13</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1054,7 +1079,7 @@
     </row>
     <row r="17" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="18"/>
@@ -1071,143 +1096,143 @@
         <v>0</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E22" s="15"/>
     </row>
     <row r="23" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E23" s="15"/>
     </row>
     <row r="24" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E24" s="15"/>
     </row>
     <row r="25" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E25" s="15"/>
     </row>
     <row r="26" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D30" s="15"/>
     </row>
@@ -1217,7 +1242,7 @@
     </row>
     <row r="32" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="18"/>
@@ -1231,233 +1256,233 @@
     </row>
     <row r="33" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C40" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1466,7 +1491,7 @@
     </row>
     <row r="55" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B55" s="22"/>
       <c r="C55" s="23"/>
@@ -1480,131 +1505,131 @@
     </row>
     <row r="56" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B57" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>58</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B58" s="15" t="s">
-        <v>70</v>
-      </c>
       <c r="C58" s="15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="37" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="13"/>
       <c r="B67" s="3"/>
       <c r="D67" s="15"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="13" t="s">
         <v>0</v>
       </c>
@@ -1638,7 +1663,7 @@
     </row>
     <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="6" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E69" s="8"/>
     </row>
@@ -4114,24 +4139,6 @@
             <xm:f>'Drop-down lists'!#REF!</xm:f>
           </x14:formula1>
           <xm:sqref>B6:B7</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
-          <x14:formula1>
-            <xm:f>'Drop-down lists'!$A$2:$A$12</xm:f>
-          </x14:formula1>
-          <xm:sqref>B5</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
-          <x14:formula1>
-            <xm:f>'Drop-down lists'!$D$2:$D$10</xm:f>
-          </x14:formula1>
-          <xm:sqref>E69:E569</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
-          <x14:formula1>
-            <xm:f>'Drop-down lists'!$E$2:$E$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>F69:F569</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
@@ -4155,7 +4162,25 @@
           <x14:formula1>
             <xm:f>'Drop-down lists'!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H167:H208 H70:H166</xm:sqref>
+          <xm:sqref>H70:H208</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
+          <x14:formula1>
+            <xm:f>'Drop-down lists'!$E$2:$E$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>F69:F569</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+          <x14:formula1>
+            <xm:f>'Drop-down lists'!$A$2:$A$15</xm:f>
+          </x14:formula1>
+          <xm:sqref>B5</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
+          <x14:formula1>
+            <xm:f>'Drop-down lists'!$D$2:$D$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>E69:E569</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4166,7 +4191,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.83203125" customWidth="1"/>
@@ -4198,10 +4223,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -4276,68 +4301,62 @@
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>38</v>
+      <c r="A6" s="26" t="s">
+        <v>121</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="3">
-        <v>3</v>
-      </c>
-      <c r="E6" s="3">
-        <v>4</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>40</v>
+      <c r="A7" s="26" t="s">
+        <v>123</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="E7" s="3">
-        <v>5</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3"/>
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="3">
+        <v>5</v>
+      </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>126</v>
       </c>
       <c r="D9" s="3">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -4346,14 +4365,12 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="3">
-        <v>5</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -4361,18 +4378,61 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>41</v>
+      </c>
+      <c r="D12" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="3">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/onprc_ehr/resources/web/onprc_ehr/templates/ClinicalProcessingTemplate.xlsx
+++ b/onprc_ehr/resources/web/onprc_ehr/templates/ClinicalProcessingTemplate.xlsx
@@ -5,20 +5,20 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/tmp/blasarVolumes/blasar/XML_Project/Heather_Panaro/ClinicalProcessing_TPR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blasar/test_25.11/server/modules/onprcEHRModules/onprc_ehr/resources/web/onprc_ehr/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67BF84A-E68A-4241-B673-2A22004E0B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC340AF-E0FD-2446-82FB-8D1B2F376D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="V0mH21jSP57WeMvfm2GZf/CFapX9PbyX3c7CLbaowv65HEOfZYZks22oton1PO1KhMKfP/Yy+b48PowhVvmdMw==" workbookSaltValue="7RYukLmSAngqyTzJhGnEpg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="10840" yWindow="1900" windowWidth="30600" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7800" yWindow="1900" windowWidth="30600" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ClinProcessing Entry Template" sheetId="6" r:id="rId1"/>
     <sheet name="Drop-down lists" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ClinProcessing Entry Template'!$A$80:$J$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ClinProcessing Entry Template'!$A$79:$J$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Drop-down lists'!$G$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -923,7 +923,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:J720"/>
+  <dimension ref="A1:J719"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.6640625" style="12" customWidth="1"/>
@@ -967,30 +967,37 @@
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="15"/>
+    <row r="6" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
     </row>
     <row r="7" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
+      <c r="A7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>87</v>
@@ -998,10 +1005,10 @@
     </row>
     <row r="9" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>87</v>
@@ -1009,10 +1016,10 @@
     </row>
     <row r="10" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>50</v>
+        <v>15</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>87</v>
@@ -1020,10 +1027,10 @@
     </row>
     <row r="11" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>47</v>
+        <v>16</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>48</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>87</v>
@@ -1031,10 +1038,10 @@
     </row>
     <row r="12" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>48</v>
+        <v>14</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>87</v>
@@ -1042,10 +1049,10 @@
     </row>
     <row r="13" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>87</v>
@@ -1053,50 +1060,50 @@
     </row>
     <row r="14" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C15" s="15" t="s">
+      <c r="B15" s="3"/>
+      <c r="D15" s="15"/>
+    </row>
+    <row r="16" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="15" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="3"/>
-      <c r="D16" s="15"/>
-    </row>
-    <row r="17" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B17" s="20"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
     </row>
     <row r="18" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C18" s="15" t="s">
         <v>87</v>
@@ -1104,10 +1111,10 @@
     </row>
     <row r="19" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>54</v>
+        <v>108</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>50</v>
       </c>
       <c r="C19" s="15" t="s">
         <v>87</v>
@@ -1115,10 +1122,10 @@
     </row>
     <row r="20" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C20" s="15" t="s">
         <v>87</v>
@@ -1126,21 +1133,22 @@
     </row>
     <row r="21" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>17</v>
+        <v>106</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>87</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="E21" s="15"/>
     </row>
     <row r="22" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>105</v>
@@ -1149,22 +1157,22 @@
     </row>
     <row r="23" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>50</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E23" s="15"/>
     </row>
     <row r="24" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>102</v>
@@ -1173,22 +1181,21 @@
     </row>
     <row r="25" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="E25" s="15"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="26" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="C26" s="15" t="s">
         <v>87</v>
@@ -1196,10 +1203,10 @@
     </row>
     <row r="27" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="C27" s="15" t="s">
         <v>87</v>
@@ -1207,10 +1214,10 @@
     </row>
     <row r="28" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="C28" s="15" t="s">
         <v>87</v>
@@ -1218,48 +1225,48 @@
     </row>
     <row r="29" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C29" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" s="15"/>
+    </row>
+    <row r="30" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="3"/>
+      <c r="D30" s="15"/>
+    </row>
+    <row r="31" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="20"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D30" s="15"/>
-    </row>
-    <row r="31" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="3"/>
-      <c r="D31" s="15"/>
-    </row>
-    <row r="32" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="20"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C33" s="15" t="s">
         <v>87</v>
@@ -1267,10 +1274,10 @@
     </row>
     <row r="34" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>54</v>
+        <v>93</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="C34" s="15" t="s">
         <v>87</v>
@@ -1278,10 +1285,10 @@
     </row>
     <row r="35" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C35" s="15" t="s">
         <v>87</v>
@@ -1289,10 +1296,10 @@
     </row>
     <row r="36" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="C36" s="15" t="s">
         <v>87</v>
@@ -1300,10 +1307,10 @@
     </row>
     <row r="37" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="12" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="C37" s="15" t="s">
         <v>87</v>
@@ -1311,43 +1318,43 @@
     </row>
     <row r="38" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>115</v>
+      <c r="A39" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>56</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C40" s="15" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>54</v>
+      <c r="A41" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="C41" s="15" t="s">
         <v>78</v>
@@ -1355,10 +1362,10 @@
     </row>
     <row r="42" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>78</v>
@@ -1366,10 +1373,10 @@
     </row>
     <row r="43" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>78</v>
@@ -1377,10 +1384,10 @@
     </row>
     <row r="44" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="C44" s="15" t="s">
         <v>78</v>
@@ -1388,10 +1395,10 @@
     </row>
     <row r="45" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>78</v>
@@ -1399,21 +1406,21 @@
     </row>
     <row r="46" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>115</v>
+        <v>77</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>56</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C47" s="15" t="s">
         <v>70</v>
@@ -1421,10 +1428,10 @@
     </row>
     <row r="48" spans="1:3" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>54</v>
+        <v>75</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="C48" s="15" t="s">
         <v>70</v>
@@ -1432,10 +1439,10 @@
     </row>
     <row r="49" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C49" s="15" t="s">
         <v>70</v>
@@ -1443,10 +1450,10 @@
     </row>
     <row r="50" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C50" s="15" t="s">
         <v>70</v>
@@ -1454,10 +1461,10 @@
     </row>
     <row r="51" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C51" s="15" t="s">
         <v>70</v>
@@ -1465,50 +1472,50 @@
     </row>
     <row r="52" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="C52" s="15" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>70</v>
-      </c>
+      <c r="B53" s="3"/>
+      <c r="D53" s="15"/>
     </row>
     <row r="54" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B54" s="3"/>
-      <c r="D54" s="15"/>
+      <c r="A54" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" s="22"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="23"/>
     </row>
     <row r="55" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B55" s="22"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="23"/>
-      <c r="I55" s="23"/>
-      <c r="J55" s="23"/>
+      <c r="A55" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="56" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>58</v>
@@ -1516,35 +1523,35 @@
     </row>
     <row r="57" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="0.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>62</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" ht="23" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B59" s="15" t="s">
-        <v>64</v>
+      <c r="B59" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -1552,51 +1559,51 @@
         <v>62</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>118</v>
+        <v>50</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="32" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="37" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>50</v>
+        <v>57</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>56</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="37" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C63" s="15" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>52</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>49</v>
@@ -1604,67 +1611,60 @@
     </row>
     <row r="65" spans="1:10" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C65" s="15" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="65" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>49</v>
-      </c>
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="13"/>
+      <c r="B66" s="3"/>
+      <c r="D66" s="15"/>
     </row>
     <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="13"/>
-      <c r="B67" s="3"/>
-      <c r="D67" s="15"/>
-    </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="13" t="s">
+      <c r="A67" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B68" s="25" t="s">
+      <c r="B67" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C68" s="25" t="s">
+      <c r="C67" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D68" s="25" t="s">
+      <c r="D67" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="E68" s="25" t="s">
+      <c r="E67" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F68" s="25" t="s">
+      <c r="F67" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="G68" s="25" t="s">
+      <c r="G67" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="H68" s="25" t="s">
+      <c r="H67" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="I68" s="25" t="s">
+      <c r="I67" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J68" s="25" t="s">
+      <c r="J67" s="25" t="s">
         <v>5</v>
       </c>
     </row>
+    <row r="68" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E68" s="8"/>
+    </row>
     <row r="69" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
-        <v>117</v>
-      </c>
+      <c r="A69" s="9"/>
       <c r="E69" s="8"/>
     </row>
     <row r="70" spans="1:10" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -3663,12 +3663,12 @@
       <c r="A568" s="9"/>
       <c r="E568" s="8"/>
     </row>
-    <row r="569" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A569" s="9"/>
-      <c r="E569" s="8"/>
+    <row r="569" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H569" s="7"/>
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H570" s="7"/>
+      <c r="I570" s="15"/>
     </row>
     <row r="571" spans="1:9" x14ac:dyDescent="0.2">
       <c r="H571" s="7"/>
@@ -3712,7 +3712,6 @@
     </row>
     <row r="581" spans="8:9" x14ac:dyDescent="0.2">
       <c r="H581" s="7"/>
-      <c r="I581" s="15"/>
     </row>
     <row r="582" spans="8:9" x14ac:dyDescent="0.2">
       <c r="H582" s="7"/>
@@ -4092,8 +4091,8 @@
     <row r="707" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H707" s="7"/>
     </row>
-    <row r="708" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H708" s="7"/>
+    <row r="709" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H709" s="15"/>
     </row>
     <row r="710" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H710" s="15"/>
@@ -4124,9 +4123,6 @@
     </row>
     <row r="719" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H719" s="15"/>
-    </row>
-    <row r="720" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H720" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4134,41 +4130,35 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
-          <x14:formula1>
-            <xm:f>'Drop-down lists'!#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>B6:B7</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000004000000}">
           <x14:formula1>
             <xm:f>'Drop-down lists'!$F$2:$F$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G69:G569</xm:sqref>
+          <xm:sqref>G68:G568</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000006000000}">
           <x14:formula1>
             <xm:f>'Drop-down lists'!$H$2:$H$3</xm:f>
           </x14:formula1>
-          <xm:sqref>I69:I569</xm:sqref>
+          <xm:sqref>I68:I568</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000005000000}">
           <x14:formula1>
             <xm:f>'Drop-down lists'!$G$2:$G$4</xm:f>
           </x14:formula1>
-          <xm:sqref>H69 H209:H708</xm:sqref>
+          <xm:sqref>H68 H208:H707</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{25E1E495-68A7-8D49-B0E7-753B3990CBA7}">
           <x14:formula1>
             <xm:f>'Drop-down lists'!$G$2:$G$5</xm:f>
           </x14:formula1>
-          <xm:sqref>H70:H208</xm:sqref>
+          <xm:sqref>H69:H207</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000003000000}">
           <x14:formula1>
             <xm:f>'Drop-down lists'!$E$2:$E$8</xm:f>
           </x14:formula1>
-          <xm:sqref>F69:F569</xm:sqref>
+          <xm:sqref>F68:F568</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
@@ -4180,7 +4170,13 @@
           <x14:formula1>
             <xm:f>'Drop-down lists'!$D$2:$D$13</xm:f>
           </x14:formula1>
-          <xm:sqref>E69:E569</xm:sqref>
+          <xm:sqref>E68:E568</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>'Drop-down lists'!#REF!</xm:f>
+          </x14:formula1>
+          <xm:sqref>B6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/onprc_ehr/resources/web/onprc_ehr/templates/ClinicalProcessingTemplate.xlsx
+++ b/onprc_ehr/resources/web/onprc_ehr/templates/ClinicalProcessingTemplate.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blasar/test_25.11/server/modules/onprcEHRModules/onprc_ehr/resources/web/onprc_ehr/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/tmp/blasarVolumes/blasar/XML_Project/Heather_Panaro/ClinicalProcessing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC340AF-E0FD-2446-82FB-8D1B2F376D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB72ACEB-576B-0C40-B1C1-E41F7050723D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="V0mH21jSP57WeMvfm2GZf/CFapX9PbyX3c7CLbaowv65HEOfZYZks22oton1PO1KhMKfP/Yy+b48PowhVvmdMw==" workbookSaltValue="7RYukLmSAngqyTzJhGnEpg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="7800" yWindow="1900" windowWidth="30600" windowHeight="18440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -928,7 +928,7 @@
   <cols>
     <col min="1" max="1" width="11.6640625" style="12" customWidth="1"/>
     <col min="2" max="2" width="37.33203125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="38.5" style="11" customWidth="1"/>
+    <col min="3" max="3" width="50.6640625" style="11" customWidth="1"/>
     <col min="4" max="4" width="26.5" style="11" customWidth="1"/>
     <col min="5" max="8" width="6.33203125" style="11" customWidth="1"/>
     <col min="9" max="9" width="4.1640625" style="11" bestFit="1" customWidth="1"/>
